--- a/inst/templates/SensitivityParameter.xlsx
+++ b/inst/templates/SensitivityParameter.xlsx
@@ -1,42 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ztcok\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1183FAD4-F54C-4CB3-BD5E-C60D7FD289F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{6A61F58B-61FD-432D-A88E-7D515FABAC84}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="Template" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="_Validity" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>model path</t>
   </si>
@@ -54,13 +32,35 @@
   </si>
   <si>
     <t>Muscle Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ParameterPath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parameter display name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model path to parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muscle Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organism|Muscle|Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated list values for Excel data validation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,16 +69,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <b/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <i/>
     </font>
   </fonts>
   <fills count="3">
@@ -448,39 +448,59 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{179C684F-1072-4717-8045-C7363713E540}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" customWidth="1"/>
-    <col min="2" max="2" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="33.85546875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="45.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/inst/templates/SensitivityParameter.xlsx
+++ b/inst/templates/SensitivityParameter.xlsx
@@ -493,13 +493,7 @@
   <cols>
     <col min="1" max="1" width="45.71" hidden="0" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
